--- a/01_analyses_states/Madhya Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Madhya Pradesh/results/SoIB_summaries.xlsx
@@ -398,11 +398,8 @@
       <c r="C2">
         <v>3</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>32.1</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +425,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>29</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>51.8</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="5">
@@ -455,11 +446,8 @@
       <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +460,10 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C8">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +675,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +691,7 @@
         <v>104</v>
       </c>
       <c r="C4">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +748,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>71.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2">
-        <v>79.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -782,16 +767,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>28.2</v>
+        <v>30.1</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>20.4</v>
+        <v>22.6</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_states/Madhya Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Madhya Pradesh/results/SoIB_summaries.xlsx
@@ -396,13 +396,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>8.300000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +425,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>26</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>54.2</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="5">
@@ -455,11 +446,8 @@
       <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +460,10 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>8.300000000000001</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C8">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +675,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +691,7 @@
         <v>104</v>
       </c>
       <c r="C4">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Madhya Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Madhya Pradesh/results/SoIB_summaries.xlsx
@@ -393,13 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
       </c>
       <c r="E2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -409,13 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
       </c>
       <c r="E3">
-        <v>27.8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -428,10 +434,13 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>57.4</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -444,10 +453,13 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="6">
@@ -460,10 +472,13 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -473,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C8">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3">
@@ -675,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -688,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C4">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -748,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2">
-        <v>69.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>77.40000000000001</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="3">
@@ -767,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3">
-        <v>30.1</v>
+        <v>31.1</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>22.6</v>
+        <v>25.3</v>
       </c>
     </row>
   </sheetData>
